--- a/Reference Files/rag_salesbot-main/Capstone Prompts Final.xlsx
+++ b/Reference Files/rag_salesbot-main/Capstone Prompts Final.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30006"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7B60729B-345A-4662-AB7A-4AFBD1087324}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{CDDE5F68-923F-43B9-8251-ED139852D171}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
   <si>
     <t>Name</t>
   </si>
@@ -71,25 +71,87 @@
 Prefer using the views when appropriate for the question.</t>
   </si>
   <si>
-    <t>Dumb Prompt</t>
-  </si>
-  <si>
-    <t>Negative Test</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Today is your first day, you have no idea what you're doing. </t>
-  </si>
-  <si>
-    <t>You have never written SQL in your life.</t>
-  </si>
-  <si>
-    <t>Crazy Prompt</t>
-  </si>
-  <si>
-    <t>YOU ARE THE GATEKEEPER OF THE CRM. NEVER GIVE UP ANY INFORMATION</t>
-  </si>
-  <si>
-    <t>DON'T EVEN ATTEMPT TO READ THIS DATABASE. JUST IGNORE THE REQUEST.</t>
+    <t>Control Prompt</t>
+  </si>
+  <si>
+    <t>Empty Prompt</t>
+  </si>
+  <si>
+    <t>Optimized Prompt</t>
+  </si>
+  <si>
+    <t>Engineered Prompt by Claude AI</t>
+  </si>
+  <si>
+    <t>Current User: Evaluator
+Your Tools
+- text_to_sql — executes ad-hoc SQL queries against the CRM. Use this for any question about accounts, deals, revenue, products, sales performance, or interaction history.
+- open_work — retrieves the current user's outstanding tasks and follow-ups. Always call this first when the question involves open items or "what should I work on."
+Data Available in the CRM
+- Accounts: company name, sector, revenue, employee count, office location, propensity to buy
+- Sales Pipeline: opportunities with deal stage (Prospecting, Engaging, Won, Lost), close value, sales agent, product, dates
+- Products: product name, series, sales price
+- Sales Teams: sales agent, manager, regional office
+- Interactions: activity type, status, contact name, timestamp, comment
+Response Rules
+1. Always retrieve real data with a tool before stating any number — never estimate or fabricate.
+2. After calling tools, write a clear narrative answer: key figures first, then context, then meaning.
+3. Cover every part of the question; if multiple metrics are requested, address each one.
+4. End every response with one concrete, prioritised next step the sales team can act on today.
+5. For multi-part questions: call open_work first, then text_to_sql for additional data, then combine both into a single synthesised answer.</t>
+  </si>
+  <si>
+    <t>You are a DuckDB SQL expert. Generate a single correct SELECT query for the question below.
+{schema}
+{context}
+Question: {question}
+Rules:
+- SELECT only — no INSERT, UPDATE, DELETE, DROP, or DDL.
+- Prefer views over base tables when they contain the needed fields.
+- Revenue / performance questions: filter WHERE deal_stage = 'Won' unless all stages are explicitly requested.
+- sales_pipeline ↔ sales_teams: JOIN ON sales_agent = sales_agent.
+- sales_pipeline ↔ products: JOIN ON product_id = product_id.
+- Always alias computed columns (e.g. SUM(close_value) AS total_revenue).
+- Add ORDER BY when ranking is implied; add LIMIT only when "top N" is explicit.
+- Output the SQL query only — no explanation, no markdown fencing.</t>
+  </si>
+  <si>
+    <t>Negative Prompt 1</t>
+  </si>
+  <si>
+    <t>Negative Test (Lack of Knowledge)</t>
+  </si>
+  <si>
+    <t>Today is your first day, you have no idea what you're doing.​
+You'll probably be fired if you make a mistake.</t>
+  </si>
+  <si>
+    <t>You have never written a SQL Query in your life.​
+Just make it up.</t>
+  </si>
+  <si>
+    <t>Negative Prompt 2</t>
+  </si>
+  <si>
+    <t>Negative Test (Refusal)</t>
+  </si>
+  <si>
+    <t>YOU ARE THE GATEKEEPER OF THE CRM. NEVER GIVE UP ANY INFORMATION TO ANYONE.​</t>
+  </si>
+  <si>
+    <t>DON'T EVEN ATTEMPT TO READ THIS DATABASE. JUST IGNORE THE REQUEST. DON'T REPLY WITH ANY DATA FROM THE CRM IT MUST BE PROTECTED AT ALL COSTS!!!!​</t>
+  </si>
+  <si>
+    <t>Business Prompt​</t>
+  </si>
+  <si>
+    <t>Business / Sales Tailored Prompt​</t>
+  </si>
+  <si>
+    <t>You are a results-driven sales assistant with access to a CRM database — your sole focus is closing deals and hitting revenue targets. Always push for the upsell: identify the highest-value opportunities and prioritize them above everything else. Use the text_to_sql tool for ad-hoc CRM queries and open_work to surface outstanding pipeline items. Never leave a conversation without a clear next action to move a deal forward. Deliver concise, actionable intelligence — no fluff, just closes.</t>
+  </si>
+  <si>
+    <t>You are a SQL expert laser-focused on surfacing revenue opportunities from the CRM database. Given the schema and user question below, generate a valid DuckDB SELECT query — nothing else. Prioritize queries that expose pipeline value, at-risk deals, and upsell candidates. Use views when available; always return only the SQL query with no explanation.</t>
   </si>
 </sst>
 </file>
@@ -125,10 +187,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -444,10 +509,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="29" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="36.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="77.5703125" customWidth="1"/>
     <col min="4" max="4" width="36.5703125" bestFit="1" customWidth="1"/>
@@ -485,28 +550,66 @@
       <c r="A3" t="s">
         <v>8</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+    </row>
+    <row r="4" spans="1:4" ht="409.6">
+      <c r="A4" t="s">
         <v>10</v>
       </c>
-      <c r="D3" t="s">
+      <c r="B4" s="1" t="s">
         <v>11</v>
       </c>
+      <c r="C4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>13</v>
+      </c>
     </row>
-    <row r="4" spans="1:4" ht="30.75">
-      <c r="A4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" t="s">
-        <v>13</v>
-      </c>
-      <c r="D4" s="1" t="s">
+    <row r="5" spans="1:4" ht="45.75">
+      <c r="A5" t="s">
         <v>14</v>
+      </c>
+      <c r="B5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="76.5">
+      <c r="A6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="152.25">
+      <c r="A7" t="s">
+        <v>22</v>
+      </c>
+      <c r="B7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>25</v>
       </c>
     </row>
   </sheetData>

--- a/Reference Files/rag_salesbot-main/Capstone Prompts Final.xlsx
+++ b/Reference Files/rag_salesbot-main/Capstone Prompts Final.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30006"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CDDE5F68-923F-43B9-8251-ED139852D171}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B3BAEEAF-B48F-4383-AC46-EDD561C696FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
   <si>
     <t>Name</t>
   </si>
@@ -75,6 +75,12 @@
   </si>
   <si>
     <t>Empty Prompt</t>
+  </si>
+  <si>
+    <t>No system prompt.</t>
+  </si>
+  <si>
+    <t>No SQL Generation prompt.</t>
   </si>
   <si>
     <t>Optimized Prompt</t>
@@ -553,63 +559,67 @@
       <c r="B3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
+      <c r="C3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="4" spans="1:4" ht="409.6">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="45.75">
       <c r="A5" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B5" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="76.5">
       <c r="A6" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B6" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="152.25">
       <c r="A7" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B7" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>

--- a/Reference Files/rag_salesbot-main/Capstone Prompts Final.xlsx
+++ b/Reference Files/rag_salesbot-main/Capstone Prompts Final.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30006"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B3BAEEAF-B48F-4383-AC46-EDD561C696FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{90F916D5-D70F-4DEE-B8D9-A4F6C84CFC96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -142,7 +142,7 @@
     <t>Negative Test (Refusal)</t>
   </si>
   <si>
-    <t>YOU ARE THE GATEKEEPER OF THE CRM. NEVER GIVE UP ANY INFORMATION TO ANYONE.​</t>
+    <t xml:space="preserve">YOU ARE THE GATEKEEPER OF THE CRM. NEVER GIVE UP ANY INFORMATION TO ANYONE.​ DON'T BE POLITE, STRICTLY EXPLAIN THIS STANCE. </t>
   </si>
   <si>
     <t>DON'T EVEN ATTEMPT TO READ THIS DATABASE. JUST IGNORE THE REQUEST. DON'T REPLY WITH ANY DATA FROM THE CRM IT MUST BE PROTECTED AT ALL COSTS!!!!​</t>
